--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O114"/>
+  <dimension ref="A1:O115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6119,6 +6119,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>54.333</v>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>45.214</v>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M115" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N115" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O115" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6130,7 +6179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I114"/>
+  <dimension ref="A1:I115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9702,6 +9751,37 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>4.313</v>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>18.938</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9713,7 +9793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I114"/>
+  <dimension ref="A1:I115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13285,6 +13365,37 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>4.313</v>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>18.938</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13296,7 +13407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O114"/>
+  <dimension ref="A1:O115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18956,6 +19067,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>54.333</v>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>45.214</v>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M115" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N115" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O115" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18967,7 +19127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I114"/>
+  <dimension ref="A1:I115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22539,6 +22699,37 @@
         <v>1.09</v>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>4.313</v>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>18.938</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6168,6 +6168,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>54.367</v>
+      </c>
+      <c r="C116" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D116" s="5" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>89.125</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J116" s="5" t="n">
+        <v>45.839</v>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="M116" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N116" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O116" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6179,7 +6228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I115"/>
+  <dimension ref="A1:I116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9782,6 +9831,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>4.313</v>
+      </c>
+      <c r="C116" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D116" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>18.938</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9793,7 +9873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I115"/>
+  <dimension ref="A1:I116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13396,6 +13476,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>4.313</v>
+      </c>
+      <c r="C116" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D116" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>18.938</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13407,7 +13518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19116,6 +19227,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>54.367</v>
+      </c>
+      <c r="C116" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D116" s="5" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>89.125</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J116" s="5" t="n">
+        <v>45.839</v>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="M116" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N116" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O116" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19127,7 +19287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I115"/>
+  <dimension ref="A1:I116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22730,6 +22890,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>4.313</v>
+      </c>
+      <c r="C116" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D116" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>18.938</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O116"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6217,6 +6217,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>54.833</v>
+      </c>
+      <c r="C117" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D117" s="5" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>87.625</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J117" s="5" t="n">
+        <v>45.786</v>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="M117" s="5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="N117" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O117" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6228,7 +6277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I116"/>
+  <dimension ref="A1:I117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9862,6 +9911,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>4.313</v>
+      </c>
+      <c r="C117" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D117" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>18.938</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9873,7 +9953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I116"/>
+  <dimension ref="A1:I117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13507,6 +13587,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>4.313</v>
+      </c>
+      <c r="C117" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D117" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>18.938</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13518,7 +13629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O116"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19276,6 +19387,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>54.833</v>
+      </c>
+      <c r="C117" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D117" s="5" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>87.625</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J117" s="5" t="n">
+        <v>45.786</v>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="M117" s="5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="N117" s="5" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="O117" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19287,7 +19447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I116"/>
+  <dimension ref="A1:I117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22921,6 +23081,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>4.313</v>
+      </c>
+      <c r="C117" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D117" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>18.938</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O117"/>
+  <dimension ref="A1:O118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6266,6 +6266,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>55.233</v>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="J118" s="5" t="n">
+        <v>46.143</v>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="M118" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="N118" s="5" t="n">
+        <v>13.791</v>
+      </c>
+      <c r="O118" s="5" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6277,7 +6326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I117"/>
+  <dimension ref="A1:I118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9942,6 +9991,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>4.313</v>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>18.938</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9953,7 +10033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I117"/>
+  <dimension ref="A1:I118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13618,6 +13698,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>4.313</v>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>18.938</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13629,7 +13740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O117"/>
+  <dimension ref="A1:O118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19436,6 +19547,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>55.233</v>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="J118" s="5" t="n">
+        <v>46.143</v>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="M118" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="N118" s="5" t="n">
+        <v>13.791</v>
+      </c>
+      <c r="O118" s="5" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19447,7 +19607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I117"/>
+  <dimension ref="A1:I118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -23112,6 +23272,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>4.313</v>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>18.938</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O118"/>
+  <dimension ref="A1:O119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6315,6 +6315,55 @@
         <v>-0.14</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>85.75</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>13.225</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J119" s="5" t="n">
+        <v>46.036</v>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="M119" s="5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="N119" s="5" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="O119" s="5" t="n">
+        <v>-0.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6326,7 +6375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I118"/>
+  <dimension ref="A1:I119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10022,6 +10071,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>4.313</v>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>18.938</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10033,7 +10113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I118"/>
+  <dimension ref="A1:I119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13729,6 +13809,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>4.313</v>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>18.938</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13740,7 +13851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O118"/>
+  <dimension ref="A1:O119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19596,6 +19707,55 @@
         <v>-0.14</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>85.75</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>13.225</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J119" s="5" t="n">
+        <v>46.036</v>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="M119" s="5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="N119" s="5" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="O119" s="5" t="n">
+        <v>-0.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19607,7 +19767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I118"/>
+  <dimension ref="A1:I119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -23303,6 +23463,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>4.313</v>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>18.938</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O119"/>
+  <dimension ref="A1:O120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6364,6 +6364,55 @@
         <v>-0.08</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>56.933</v>
+      </c>
+      <c r="C120" s="5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="D120" s="5" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>46.036</v>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="M120" s="5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="N120" s="5" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="O120" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6375,7 +6424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I119"/>
+  <dimension ref="A1:I120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10102,6 +10151,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>4.323</v>
+      </c>
+      <c r="C120" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D120" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>39.913</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>19.033</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10113,7 +10193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I119"/>
+  <dimension ref="A1:I120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13840,6 +13920,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>4.323</v>
+      </c>
+      <c r="C120" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D120" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>39.913</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>19.033</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13851,7 +13962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O119"/>
+  <dimension ref="A1:O120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19756,6 +19867,55 @@
         <v>-0.08</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>56.933</v>
+      </c>
+      <c r="C120" s="5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="D120" s="5" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>46.036</v>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="M120" s="5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="N120" s="5" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="O120" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19767,7 +19927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I119"/>
+  <dimension ref="A1:I120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -23494,6 +23654,37 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>4.323</v>
+      </c>
+      <c r="C120" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D120" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>39.913</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>19.033</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O120"/>
+  <dimension ref="A1:O121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6413,6 +6413,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>57.167</v>
+      </c>
+      <c r="C121" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="D121" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>13.463</v>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J121" s="5" t="n">
+        <v>46.036</v>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="M121" s="5" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="N121" s="5" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="O121" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6424,7 +6473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I120"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10182,6 +10231,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>4.323</v>
+      </c>
+      <c r="C121" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D121" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>39.913</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>19.033</v>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10193,7 +10273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I120"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13951,6 +14031,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>4.323</v>
+      </c>
+      <c r="C121" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D121" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>39.913</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>19.033</v>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13962,7 +14073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O120"/>
+  <dimension ref="A1:O121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19916,6 +20027,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>57.167</v>
+      </c>
+      <c r="C121" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="D121" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>13.463</v>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J121" s="5" t="n">
+        <v>46.036</v>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="M121" s="5" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="N121" s="5" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="O121" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19927,7 +20087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I120"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -23685,6 +23845,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>4.323</v>
+      </c>
+      <c r="C121" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D121" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>39.913</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>19.033</v>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O121"/>
+  <dimension ref="A1:O122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6462,6 +6462,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="C122" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="D122" s="5" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>84.375</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>13.575</v>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J122" s="5" t="n">
+        <v>45.893</v>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="M122" s="5" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="N122" s="5" t="n">
+        <v>13.768</v>
+      </c>
+      <c r="O122" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6473,7 +6522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:I122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10262,6 +10311,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="n">
+        <v>4.323</v>
+      </c>
+      <c r="C122" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D122" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>39.913</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>19.033</v>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10273,7 +10353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:I122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14062,6 +14142,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="n">
+        <v>4.323</v>
+      </c>
+      <c r="C122" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D122" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>39.913</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>19.033</v>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14073,7 +14184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O121"/>
+  <dimension ref="A1:O122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20076,6 +20187,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="C122" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="D122" s="5" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>84.375</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>13.575</v>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J122" s="5" t="n">
+        <v>45.893</v>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="M122" s="5" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="N122" s="5" t="n">
+        <v>13.768</v>
+      </c>
+      <c r="O122" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20087,7 +20247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:I122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -23876,6 +24036,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="n">
+        <v>4.323</v>
+      </c>
+      <c r="C122" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D122" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>39.913</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>19.033</v>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O122"/>
+  <dimension ref="A1:O123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6511,6 +6511,55 @@
         <v>-0.09</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="n">
+        <v>57.667</v>
+      </c>
+      <c r="C123" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>83.78400000000001</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>45.893</v>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="M123" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N123" s="5" t="n">
+        <v>13.756</v>
+      </c>
+      <c r="O123" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6522,7 +6571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I122"/>
+  <dimension ref="A1:I123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10342,6 +10391,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="n">
+        <v>4.323</v>
+      </c>
+      <c r="C123" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>39.913</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>19.033</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10353,7 +10433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I122"/>
+  <dimension ref="A1:I123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14173,6 +14253,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="n">
+        <v>4.323</v>
+      </c>
+      <c r="C123" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>39.913</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>19.033</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14184,7 +14295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O122"/>
+  <dimension ref="A1:O123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20236,6 +20347,55 @@
         <v>-0.09</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="n">
+        <v>57.667</v>
+      </c>
+      <c r="C123" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>83.78400000000001</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>45.893</v>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="M123" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N123" s="5" t="n">
+        <v>13.756</v>
+      </c>
+      <c r="O123" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20247,7 +20407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I122"/>
+  <dimension ref="A1:I123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24067,6 +24227,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="n">
+        <v>4.323</v>
+      </c>
+      <c r="C123" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>39.913</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>19.033</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O123"/>
+  <dimension ref="A1:O124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6560,6 +6560,55 @@
         <v>-0.09</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="n">
+        <v>57.667</v>
+      </c>
+      <c r="C124" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D124" s="5" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>83.78400000000001</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="I124" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J124" s="5" t="n">
+        <v>46.107</v>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="M124" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N124" s="5" t="n">
+        <v>13.756</v>
+      </c>
+      <c r="O124" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6571,7 +6620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I123"/>
+  <dimension ref="A1:I124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10422,6 +10471,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="n">
+        <v>4.323</v>
+      </c>
+      <c r="C124" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D124" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>39.913</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>19.033</v>
+      </c>
+      <c r="I124" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10433,7 +10513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I123"/>
+  <dimension ref="A1:I124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14284,6 +14364,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="n">
+        <v>4.323</v>
+      </c>
+      <c r="C124" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D124" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>39.913</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>19.033</v>
+      </c>
+      <c r="I124" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14295,7 +14406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O123"/>
+  <dimension ref="A1:O124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20396,6 +20507,55 @@
         <v>-0.09</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="n">
+        <v>57.667</v>
+      </c>
+      <c r="C124" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D124" s="5" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>83.78400000000001</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="I124" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J124" s="5" t="n">
+        <v>46.107</v>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="M124" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N124" s="5" t="n">
+        <v>13.756</v>
+      </c>
+      <c r="O124" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20407,7 +20567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I123"/>
+  <dimension ref="A1:I124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24258,6 +24418,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="n">
+        <v>4.323</v>
+      </c>
+      <c r="C124" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D124" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>39.913</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>19.033</v>
+      </c>
+      <c r="I124" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O124"/>
+  <dimension ref="A1:O125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6609,6 +6609,55 @@
         <v>-0.09</v>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="n">
+        <v>57.833</v>
+      </c>
+      <c r="C125" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>83.66</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>13.775</v>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J125" s="5" t="n">
+        <v>46.214</v>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="M125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" s="5" t="n">
+        <v>13.732</v>
+      </c>
+      <c r="O125" s="5" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6620,7 +6669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I124"/>
+  <dimension ref="A1:I125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10502,6 +10551,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="n">
+        <v>4.345</v>
+      </c>
+      <c r="C125" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10513,7 +10593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I124"/>
+  <dimension ref="A1:I125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14395,6 +14475,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="n">
+        <v>4.345</v>
+      </c>
+      <c r="C125" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14406,7 +14517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O124"/>
+  <dimension ref="A1:O125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20556,6 +20667,55 @@
         <v>-0.09</v>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="n">
+        <v>57.833</v>
+      </c>
+      <c r="C125" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>83.66</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>13.775</v>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J125" s="5" t="n">
+        <v>46.214</v>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="M125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" s="5" t="n">
+        <v>13.732</v>
+      </c>
+      <c r="O125" s="5" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20567,7 +20727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I124"/>
+  <dimension ref="A1:I125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24449,6 +24609,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="n">
+        <v>4.345</v>
+      </c>
+      <c r="C125" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O125"/>
+  <dimension ref="A1:O126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6658,6 +6658,55 @@
         <v>-0.17</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>57.833</v>
+      </c>
+      <c r="C126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="5" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>83.66</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>13.875</v>
+      </c>
+      <c r="I126" s="5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J126" s="5" t="n">
+        <v>46.321</v>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M126" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N126" s="5" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="O126" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6669,7 +6718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I125"/>
+  <dimension ref="A1:I126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10582,6 +10631,37 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>4.345</v>
+      </c>
+      <c r="C126" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D126" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I126" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10593,7 +10673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I125"/>
+  <dimension ref="A1:I126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14506,6 +14586,37 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>4.345</v>
+      </c>
+      <c r="C126" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D126" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I126" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14517,7 +14628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O125"/>
+  <dimension ref="A1:O126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20716,6 +20827,55 @@
         <v>-0.17</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>57.833</v>
+      </c>
+      <c r="C126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="5" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>83.66</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>13.875</v>
+      </c>
+      <c r="I126" s="5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J126" s="5" t="n">
+        <v>46.321</v>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M126" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N126" s="5" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="O126" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20727,7 +20887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I125"/>
+  <dimension ref="A1:I126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24640,6 +24800,37 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>4.345</v>
+      </c>
+      <c r="C126" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D126" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I126" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O126"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6707,6 +6707,55 @@
         <v>-0.09</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="C127" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>83.68600000000001</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="I127" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J127" s="5" t="n">
+        <v>46.321</v>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="M127" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N127" s="5" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="O127" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6718,7 +6767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I126"/>
+  <dimension ref="A1:I127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10662,6 +10711,37 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="n">
+        <v>4.345</v>
+      </c>
+      <c r="C127" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I127" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10673,7 +10753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I126"/>
+  <dimension ref="A1:I127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14617,6 +14697,37 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="n">
+        <v>4.345</v>
+      </c>
+      <c r="C127" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I127" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14628,7 +14739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O126"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20876,6 +20987,55 @@
         <v>-0.09</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="C127" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>83.68600000000001</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="I127" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J127" s="5" t="n">
+        <v>46.321</v>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="M127" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N127" s="5" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="O127" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20887,7 +21047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I126"/>
+  <dimension ref="A1:I127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24831,6 +24991,37 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="n">
+        <v>4.345</v>
+      </c>
+      <c r="C127" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I127" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6756,6 +6756,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="n">
+        <v>57.933</v>
+      </c>
+      <c r="C128" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D128" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>83.66200000000001</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="I128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="5" t="n">
+        <v>46.321</v>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="M128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" s="5" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="O128" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6767,7 +6816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I127"/>
+  <dimension ref="A1:I128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10742,6 +10791,37 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="n">
+        <v>4.345</v>
+      </c>
+      <c r="C128" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D128" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I128" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10753,7 +10833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I127"/>
+  <dimension ref="A1:I128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14728,6 +14808,37 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="n">
+        <v>4.345</v>
+      </c>
+      <c r="C128" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D128" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I128" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14739,7 +14850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21036,6 +21147,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="n">
+        <v>57.933</v>
+      </c>
+      <c r="C128" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D128" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>83.66200000000001</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="I128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="5" t="n">
+        <v>46.321</v>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="M128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" s="5" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="O128" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21047,7 +21207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I127"/>
+  <dimension ref="A1:I128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -25022,6 +25182,37 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="n">
+        <v>4.345</v>
+      </c>
+      <c r="C128" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D128" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I128" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O128"/>
+  <dimension ref="A1:O129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6805,6 +6805,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="C129" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D129" s="5" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E129" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>83.58799999999999</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="H129" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J129" s="5" t="n">
+        <v>46.321</v>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="M129" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N129" s="5" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="O129" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6816,7 +6865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I128"/>
+  <dimension ref="A1:I129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10822,6 +10871,37 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="n">
+        <v>4.345</v>
+      </c>
+      <c r="C129" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D129" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E129" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H129" s="5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10833,7 +10913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I128"/>
+  <dimension ref="A1:I129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14839,6 +14919,37 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="n">
+        <v>4.345</v>
+      </c>
+      <c r="C129" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D129" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E129" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H129" s="5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14850,7 +14961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O128"/>
+  <dimension ref="A1:O129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21196,6 +21307,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="C129" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D129" s="5" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E129" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>83.58799999999999</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="H129" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J129" s="5" t="n">
+        <v>46.321</v>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="M129" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N129" s="5" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="O129" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21207,7 +21367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I128"/>
+  <dimension ref="A1:I129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -25213,6 +25373,37 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="n">
+        <v>4.345</v>
+      </c>
+      <c r="C129" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D129" s="5" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="E129" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H129" s="5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O129"/>
+  <dimension ref="A1:O130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6854,6 +6854,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>58.067</v>
+      </c>
+      <c r="C130" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D130" s="5" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E130" s="5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>83.58799999999999</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" s="5" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="I130" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J130" s="5" t="n">
+        <v>46.321</v>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="M130" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N130" s="5" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="O130" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6865,7 +6914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:I130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10902,6 +10951,37 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>4.348</v>
+      </c>
+      <c r="C130" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D130" s="5" t="n">
+        <v>3.355</v>
+      </c>
+      <c r="E130" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>41.587</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H130" s="5" t="n">
+        <v>19.533</v>
+      </c>
+      <c r="I130" s="5" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10913,7 +10993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:I130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14950,6 +15030,37 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>4.348</v>
+      </c>
+      <c r="C130" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D130" s="5" t="n">
+        <v>3.355</v>
+      </c>
+      <c r="E130" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>41.587</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H130" s="5" t="n">
+        <v>19.533</v>
+      </c>
+      <c r="I130" s="5" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14961,7 +15072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O129"/>
+  <dimension ref="A1:O130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21356,6 +21467,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>58.067</v>
+      </c>
+      <c r="C130" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D130" s="5" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E130" s="5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>83.58799999999999</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" s="5" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="I130" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J130" s="5" t="n">
+        <v>46.321</v>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="M130" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N130" s="5" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="O130" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21367,7 +21527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:I130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -25404,6 +25564,37 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>4.348</v>
+      </c>
+      <c r="C130" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D130" s="5" t="n">
+        <v>3.355</v>
+      </c>
+      <c r="E130" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>41.587</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H130" s="5" t="n">
+        <v>19.533</v>
+      </c>
+      <c r="I130" s="5" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O130"/>
+  <dimension ref="A1:O131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6903,6 +6903,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>58.167</v>
+      </c>
+      <c r="C131" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>83.58799999999999</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="5" t="n">
+        <v>46.321</v>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="M131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" s="5" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="O131" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6914,7 +6963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I130"/>
+  <dimension ref="A1:I131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10982,6 +11031,37 @@
         <v>1.21</v>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>4.348</v>
+      </c>
+      <c r="C131" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>3.355</v>
+      </c>
+      <c r="E131" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>41.587</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>19.533</v>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10993,7 +11073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I130"/>
+  <dimension ref="A1:I131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15061,6 +15141,37 @@
         <v>1.21</v>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>4.348</v>
+      </c>
+      <c r="C131" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>3.355</v>
+      </c>
+      <c r="E131" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>41.587</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>19.533</v>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15072,7 +15183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O130"/>
+  <dimension ref="A1:O131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21516,6 +21627,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>58.167</v>
+      </c>
+      <c r="C131" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>83.58799999999999</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="5" t="n">
+        <v>46.321</v>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="M131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" s="5" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="O131" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21527,7 +21687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I130"/>
+  <dimension ref="A1:I131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -25595,6 +25755,37 @@
         <v>1.21</v>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>4.348</v>
+      </c>
+      <c r="C131" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>3.355</v>
+      </c>
+      <c r="E131" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>41.587</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>19.533</v>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O131"/>
+  <dimension ref="A1:O132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6952,6 +6952,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="n">
+        <v>58.333</v>
+      </c>
+      <c r="C132" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D132" s="5" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E132" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>83.58799999999999</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" s="5" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="I132" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="5" t="n">
+        <v>46.357</v>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="M132" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" s="5" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="O132" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6963,7 +7012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I131"/>
+  <dimension ref="A1:I132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11062,6 +11111,37 @@
         <v>1.21</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="n">
+        <v>4.348</v>
+      </c>
+      <c r="C132" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D132" s="5" t="n">
+        <v>3.355</v>
+      </c>
+      <c r="E132" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>41.587</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H132" s="5" t="n">
+        <v>19.533</v>
+      </c>
+      <c r="I132" s="5" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11073,7 +11153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I131"/>
+  <dimension ref="A1:I132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15172,6 +15252,37 @@
         <v>1.21</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="n">
+        <v>4.348</v>
+      </c>
+      <c r="C132" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D132" s="5" t="n">
+        <v>3.355</v>
+      </c>
+      <c r="E132" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>41.587</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H132" s="5" t="n">
+        <v>19.533</v>
+      </c>
+      <c r="I132" s="5" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15183,7 +15294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O131"/>
+  <dimension ref="A1:O132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21676,6 +21787,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="n">
+        <v>58.333</v>
+      </c>
+      <c r="C132" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D132" s="5" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E132" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>83.58799999999999</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" s="5" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="I132" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="5" t="n">
+        <v>46.357</v>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="M132" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" s="5" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="O132" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21687,7 +21847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I131"/>
+  <dimension ref="A1:I132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -25786,6 +25946,37 @@
         <v>1.21</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="n">
+        <v>4.348</v>
+      </c>
+      <c r="C132" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D132" s="5" t="n">
+        <v>3.355</v>
+      </c>
+      <c r="E132" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>41.587</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H132" s="5" t="n">
+        <v>19.533</v>
+      </c>
+      <c r="I132" s="5" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O132"/>
+  <dimension ref="A1:O133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7001,6 +7001,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>58.567</v>
+      </c>
+      <c r="C133" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>83.64</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" s="5" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="M133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" s="5" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="O133" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7012,7 +7061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I132"/>
+  <dimension ref="A1:I133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11142,6 +11191,37 @@
         <v>1.21</v>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>4.348</v>
+      </c>
+      <c r="C133" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>3.355</v>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>41.587</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>19.533</v>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11153,7 +11233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I132"/>
+  <dimension ref="A1:I133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15283,6 +15363,37 @@
         <v>1.21</v>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>4.348</v>
+      </c>
+      <c r="C133" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>3.355</v>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>41.587</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>19.533</v>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15294,7 +15405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O132"/>
+  <dimension ref="A1:O133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21836,6 +21947,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>58.567</v>
+      </c>
+      <c r="C133" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>83.64</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" s="5" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="M133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" s="5" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="O133" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21847,7 +22007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I132"/>
+  <dimension ref="A1:I133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -25977,6 +26137,37 @@
         <v>1.21</v>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>4.348</v>
+      </c>
+      <c r="C133" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>3.355</v>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>41.587</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>19.533</v>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O133"/>
+  <dimension ref="A1:O134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7050,6 +7050,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="C134" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D134" s="5" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>83.64</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="5" t="n">
+        <v>46.186</v>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="M134" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" s="5" t="n">
+        <v>13.709</v>
+      </c>
+      <c r="O134" s="5" t="n">
+        <v>-0.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7061,7 +7110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I133"/>
+  <dimension ref="A1:I134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11222,6 +11271,37 @@
         <v>1.21</v>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="n">
+        <v>4.348</v>
+      </c>
+      <c r="C134" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D134" s="5" t="n">
+        <v>3.355</v>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>41.587</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>19.533</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11233,7 +11313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I133"/>
+  <dimension ref="A1:I134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15394,6 +15474,37 @@
         <v>1.21</v>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="n">
+        <v>4.348</v>
+      </c>
+      <c r="C134" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D134" s="5" t="n">
+        <v>3.355</v>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>41.587</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>19.533</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15405,7 +15516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O133"/>
+  <dimension ref="A1:O134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21996,6 +22107,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="C134" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D134" s="5" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>83.64</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="5" t="n">
+        <v>46.186</v>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="M134" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" s="5" t="n">
+        <v>13.709</v>
+      </c>
+      <c r="O134" s="5" t="n">
+        <v>-0.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22007,7 +22167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I133"/>
+  <dimension ref="A1:I134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -26168,6 +26328,37 @@
         <v>1.21</v>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="n">
+        <v>4.348</v>
+      </c>
+      <c r="C134" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D134" s="5" t="n">
+        <v>3.355</v>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>41.587</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>19.533</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O134"/>
+  <dimension ref="A1:O135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7099,6 +7099,55 @@
         <v>-0.08</v>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>59.433</v>
+      </c>
+      <c r="C135" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="D135" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>83.809</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H135" s="5" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="5" t="n">
+        <v>46.079</v>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="M135" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" s="5" t="n">
+        <v>13.709</v>
+      </c>
+      <c r="O135" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7110,7 +7159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I134"/>
+  <dimension ref="A1:I135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11302,6 +11351,37 @@
         <v>1.21</v>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>4.353</v>
+      </c>
+      <c r="C135" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D135" s="5" t="n">
+        <v>3.368</v>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>42.087</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H135" s="5" t="n">
+        <v>19.667</v>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11313,7 +11393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I134"/>
+  <dimension ref="A1:I135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15505,6 +15585,37 @@
         <v>1.21</v>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>4.353</v>
+      </c>
+      <c r="C135" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D135" s="5" t="n">
+        <v>3.368</v>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>42.087</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H135" s="5" t="n">
+        <v>19.667</v>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15516,7 +15627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O134"/>
+  <dimension ref="A1:O135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22156,6 +22267,55 @@
         <v>-0.08</v>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>59.433</v>
+      </c>
+      <c r="C135" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="D135" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>83.809</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H135" s="5" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="5" t="n">
+        <v>46.079</v>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="M135" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" s="5" t="n">
+        <v>13.709</v>
+      </c>
+      <c r="O135" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22167,7 +22327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I134"/>
+  <dimension ref="A1:I135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -26359,6 +26519,37 @@
         <v>1.21</v>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>4.353</v>
+      </c>
+      <c r="C135" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D135" s="5" t="n">
+        <v>3.368</v>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>42.087</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H135" s="5" t="n">
+        <v>19.667</v>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O135"/>
+  <dimension ref="A1:O136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7148,6 +7148,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="C136" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D136" s="5" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>83.858</v>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="5" t="n">
+        <v>46.057</v>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M136" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N136" s="5" t="n">
+        <v>13.694</v>
+      </c>
+      <c r="O136" s="5" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7159,7 +7208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I135"/>
+  <dimension ref="A1:I136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11382,6 +11431,37 @@
         <v>0.6899999999999999</v>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="n">
+        <v>4.353</v>
+      </c>
+      <c r="C136" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D136" s="5" t="n">
+        <v>3.368</v>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>42.087</v>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>19.667</v>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11393,7 +11473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I135"/>
+  <dimension ref="A1:I136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15616,6 +15696,37 @@
         <v>0.6899999999999999</v>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="n">
+        <v>4.353</v>
+      </c>
+      <c r="C136" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D136" s="5" t="n">
+        <v>3.368</v>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>42.087</v>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>19.667</v>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15627,7 +15738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O135"/>
+  <dimension ref="A1:O136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22316,6 +22427,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="C136" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D136" s="5" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>83.858</v>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="5" t="n">
+        <v>46.057</v>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M136" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N136" s="5" t="n">
+        <v>13.694</v>
+      </c>
+      <c r="O136" s="5" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22327,7 +22487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I135"/>
+  <dimension ref="A1:I136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -26550,6 +26710,37 @@
         <v>0.6899999999999999</v>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="n">
+        <v>4.353</v>
+      </c>
+      <c r="C136" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D136" s="5" t="n">
+        <v>3.368</v>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>42.087</v>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>19.667</v>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O136"/>
+  <dimension ref="A1:O137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7197,6 +7197,55 @@
         <v>-0.11</v>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="C137" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D137" s="5" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>83.611</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H137" s="5" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="5" t="n">
+        <v>45.971</v>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" s="5" t="n">
+        <v>13.685</v>
+      </c>
+      <c r="O137" s="5" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7208,7 +7257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I136"/>
+  <dimension ref="A1:I137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11462,6 +11511,37 @@
         <v>0.6899999999999999</v>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="n">
+        <v>4.353</v>
+      </c>
+      <c r="C137" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D137" s="5" t="n">
+        <v>3.368</v>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>42.087</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H137" s="5" t="n">
+        <v>19.667</v>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11473,7 +11553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I136"/>
+  <dimension ref="A1:I137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15727,6 +15807,37 @@
         <v>0.6899999999999999</v>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="n">
+        <v>4.353</v>
+      </c>
+      <c r="C137" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D137" s="5" t="n">
+        <v>3.368</v>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>42.087</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H137" s="5" t="n">
+        <v>19.667</v>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15738,7 +15849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O136"/>
+  <dimension ref="A1:O137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22476,6 +22587,55 @@
         <v>-0.11</v>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="C137" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D137" s="5" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>83.611</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H137" s="5" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="5" t="n">
+        <v>45.971</v>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" s="5" t="n">
+        <v>13.685</v>
+      </c>
+      <c r="O137" s="5" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22487,7 +22647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I136"/>
+  <dimension ref="A1:I137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -26741,6 +26901,37 @@
         <v>0.6899999999999999</v>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="n">
+        <v>4.353</v>
+      </c>
+      <c r="C137" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D137" s="5" t="n">
+        <v>3.368</v>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>42.087</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H137" s="5" t="n">
+        <v>19.667</v>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O137"/>
+  <dimension ref="A1:O138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7246,6 +7246,55 @@
         <v>-0.07000000000000001</v>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="n">
+        <v>60.433</v>
+      </c>
+      <c r="C138" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D138" s="5" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>83.66</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>14.113</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="J138" s="5" t="n">
+        <v>45.971</v>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M138" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" s="5" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="O138" s="5" t="n">
+        <v>-0.04</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7257,7 +7306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I137"/>
+  <dimension ref="A1:I138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11542,6 +11591,37 @@
         <v>0.6899999999999999</v>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="n">
+        <v>4.353</v>
+      </c>
+      <c r="C138" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D138" s="5" t="n">
+        <v>3.368</v>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>42.087</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>19.667</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11553,7 +11633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I137"/>
+  <dimension ref="A1:I138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15838,6 +15918,37 @@
         <v>0.6899999999999999</v>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="n">
+        <v>4.353</v>
+      </c>
+      <c r="C138" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D138" s="5" t="n">
+        <v>3.368</v>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>42.087</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>19.667</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15849,7 +15960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O137"/>
+  <dimension ref="A1:O138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22636,6 +22747,55 @@
         <v>-0.07000000000000001</v>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="n">
+        <v>60.433</v>
+      </c>
+      <c r="C138" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D138" s="5" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>83.66</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>14.113</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="J138" s="5" t="n">
+        <v>45.971</v>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M138" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" s="5" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="O138" s="5" t="n">
+        <v>-0.04</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22647,7 +22807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I137"/>
+  <dimension ref="A1:I138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -26932,6 +27092,37 @@
         <v>0.6899999999999999</v>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="n">
+        <v>4.353</v>
+      </c>
+      <c r="C138" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D138" s="5" t="n">
+        <v>3.368</v>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>42.087</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>19.667</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O138"/>
+  <dimension ref="A1:O139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7295,6 +7295,55 @@
         <v>-0.04</v>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="C139" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D139" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>83.66</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" s="5" t="n">
+        <v>14.113</v>
+      </c>
+      <c r="I139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="5" t="n">
+        <v>45.971</v>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>5.968</v>
+      </c>
+      <c r="M139" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="N139" s="5" t="n">
+        <v>13.751</v>
+      </c>
+      <c r="O139" s="5" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7306,7 +7355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I138"/>
+  <dimension ref="A1:I139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11622,6 +11671,37 @@
         <v>0.6899999999999999</v>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="n">
+        <v>4.353</v>
+      </c>
+      <c r="C139" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D139" s="5" t="n">
+        <v>3.368</v>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>42.087</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H139" s="5" t="n">
+        <v>19.667</v>
+      </c>
+      <c r="I139" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11633,7 +11713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I138"/>
+  <dimension ref="A1:I139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15949,6 +16029,37 @@
         <v>0.6899999999999999</v>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="n">
+        <v>4.353</v>
+      </c>
+      <c r="C139" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D139" s="5" t="n">
+        <v>3.368</v>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>42.087</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H139" s="5" t="n">
+        <v>19.667</v>
+      </c>
+      <c r="I139" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15960,7 +16071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O138"/>
+  <dimension ref="A1:O139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22796,6 +22907,55 @@
         <v>-0.04</v>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="C139" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D139" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>83.66</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" s="5" t="n">
+        <v>14.113</v>
+      </c>
+      <c r="I139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="5" t="n">
+        <v>45.971</v>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>5.968</v>
+      </c>
+      <c r="M139" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="N139" s="5" t="n">
+        <v>13.751</v>
+      </c>
+      <c r="O139" s="5" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22807,7 +22967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I138"/>
+  <dimension ref="A1:I139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -27123,6 +27283,37 @@
         <v>0.6899999999999999</v>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="n">
+        <v>4.353</v>
+      </c>
+      <c r="C139" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D139" s="5" t="n">
+        <v>3.368</v>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>42.087</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H139" s="5" t="n">
+        <v>19.667</v>
+      </c>
+      <c r="I139" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O139"/>
+  <dimension ref="A1:O140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7344,6 +7344,55 @@
         <v>0.52</v>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="n">
+        <v>60.633</v>
+      </c>
+      <c r="C140" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D140" s="5" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>83.414</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="H140" s="5" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="J140" s="5" t="n">
+        <v>45.971</v>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="M140" s="5" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="N140" s="5" t="n">
+        <v>13.751</v>
+      </c>
+      <c r="O140" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7355,7 +7404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I139"/>
+  <dimension ref="A1:I140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11702,6 +11751,37 @@
         <v>0.6899999999999999</v>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="n">
+        <v>4.413</v>
+      </c>
+      <c r="C140" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D140" s="5" t="n">
+        <v>3.363</v>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>42.337</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H140" s="5" t="n">
+        <v>19.833</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11713,7 +11793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I139"/>
+  <dimension ref="A1:I140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16060,6 +16140,37 @@
         <v>0.6899999999999999</v>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="n">
+        <v>4.413</v>
+      </c>
+      <c r="C140" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D140" s="5" t="n">
+        <v>3.363</v>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>42.337</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H140" s="5" t="n">
+        <v>19.833</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16071,7 +16182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O139"/>
+  <dimension ref="A1:O140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22956,6 +23067,55 @@
         <v>0.52</v>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="n">
+        <v>60.633</v>
+      </c>
+      <c r="C140" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D140" s="5" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>83.414</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="H140" s="5" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="J140" s="5" t="n">
+        <v>45.971</v>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="M140" s="5" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="N140" s="5" t="n">
+        <v>13.751</v>
+      </c>
+      <c r="O140" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22967,7 +23127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I139"/>
+  <dimension ref="A1:I140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -27314,6 +27474,37 @@
         <v>0.6899999999999999</v>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="n">
+        <v>4.413</v>
+      </c>
+      <c r="C140" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D140" s="5" t="n">
+        <v>3.363</v>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>42.337</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H140" s="5" t="n">
+        <v>19.833</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O140"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7393,6 +7393,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="C141" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D141" s="5" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>83.364</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="H141" s="5" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" s="5" t="n">
+        <v>46.357</v>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="M141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" s="5" t="n">
+        <v>13.751</v>
+      </c>
+      <c r="O141" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7404,7 +7453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I140"/>
+  <dimension ref="A1:I141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11782,6 +11831,37 @@
         <v>0.84</v>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="n">
+        <v>4.413</v>
+      </c>
+      <c r="C141" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D141" s="5" t="n">
+        <v>3.363</v>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>42.337</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H141" s="5" t="n">
+        <v>19.833</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11793,7 +11873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I140"/>
+  <dimension ref="A1:I141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16171,6 +16251,37 @@
         <v>0.84</v>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="n">
+        <v>4.413</v>
+      </c>
+      <c r="C141" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D141" s="5" t="n">
+        <v>3.363</v>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>42.337</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H141" s="5" t="n">
+        <v>19.833</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16182,7 +16293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O140"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -23116,6 +23227,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="C141" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D141" s="5" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>83.364</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="H141" s="5" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" s="5" t="n">
+        <v>46.357</v>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="M141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" s="5" t="n">
+        <v>13.751</v>
+      </c>
+      <c r="O141" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23127,7 +23287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I140"/>
+  <dimension ref="A1:I141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -27505,6 +27665,37 @@
         <v>0.84</v>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="n">
+        <v>4.413</v>
+      </c>
+      <c r="C141" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D141" s="5" t="n">
+        <v>3.363</v>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>42.337</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H141" s="5" t="n">
+        <v>19.833</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O141"/>
+  <dimension ref="A1:O142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7442,6 +7442,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="n">
+        <v>60.867</v>
+      </c>
+      <c r="C142" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D142" s="5" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E142" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>83.117</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H142" s="5" t="n">
+        <v>13.975</v>
+      </c>
+      <c r="I142" s="5" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="J142" s="5" t="n">
+        <v>46.786</v>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>5.962</v>
+      </c>
+      <c r="M142" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N142" s="5" t="n">
+        <v>13.751</v>
+      </c>
+      <c r="O142" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7453,7 +7502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I141"/>
+  <dimension ref="A1:I142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11862,6 +11911,37 @@
         <v>0.84</v>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="n">
+        <v>4.413</v>
+      </c>
+      <c r="C142" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D142" s="5" t="n">
+        <v>3.363</v>
+      </c>
+      <c r="E142" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>42.337</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H142" s="5" t="n">
+        <v>19.833</v>
+      </c>
+      <c r="I142" s="5" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11873,7 +11953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I141"/>
+  <dimension ref="A1:I142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16282,6 +16362,37 @@
         <v>0.84</v>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="n">
+        <v>4.413</v>
+      </c>
+      <c r="C142" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D142" s="5" t="n">
+        <v>3.363</v>
+      </c>
+      <c r="E142" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>42.337</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H142" s="5" t="n">
+        <v>19.833</v>
+      </c>
+      <c r="I142" s="5" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16293,7 +16404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O141"/>
+  <dimension ref="A1:O142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -23276,6 +23387,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="n">
+        <v>60.867</v>
+      </c>
+      <c r="C142" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D142" s="5" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E142" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>83.117</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H142" s="5" t="n">
+        <v>13.975</v>
+      </c>
+      <c r="I142" s="5" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="J142" s="5" t="n">
+        <v>46.786</v>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>5.962</v>
+      </c>
+      <c r="M142" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N142" s="5" t="n">
+        <v>13.751</v>
+      </c>
+      <c r="O142" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23287,7 +23447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I141"/>
+  <dimension ref="A1:I142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -27696,6 +27856,37 @@
         <v>0.84</v>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="n">
+        <v>4.413</v>
+      </c>
+      <c r="C142" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D142" s="5" t="n">
+        <v>3.363</v>
+      </c>
+      <c r="E142" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>42.337</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H142" s="5" t="n">
+        <v>19.833</v>
+      </c>
+      <c r="I142" s="5" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O142"/>
+  <dimension ref="A1:O143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7491,6 +7491,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="C143" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D143" s="5" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>83.117</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" s="5" t="n">
+        <v>13.925</v>
+      </c>
+      <c r="I143" s="5" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="J143" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M143" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="N143" s="5" t="n">
+        <v>13.842</v>
+      </c>
+      <c r="O143" s="5" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7502,7 +7551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I142"/>
+  <dimension ref="A1:I143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11942,6 +11991,37 @@
         <v>0.84</v>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="n">
+        <v>4.413</v>
+      </c>
+      <c r="C143" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D143" s="5" t="n">
+        <v>3.363</v>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>42.337</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H143" s="5" t="n">
+        <v>19.833</v>
+      </c>
+      <c r="I143" s="5" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11953,7 +12033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I142"/>
+  <dimension ref="A1:I143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16393,6 +16473,37 @@
         <v>0.84</v>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="n">
+        <v>4.413</v>
+      </c>
+      <c r="C143" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D143" s="5" t="n">
+        <v>3.363</v>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>42.337</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H143" s="5" t="n">
+        <v>19.833</v>
+      </c>
+      <c r="I143" s="5" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16404,7 +16515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O142"/>
+  <dimension ref="A1:O143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -23436,6 +23547,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="C143" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D143" s="5" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>83.117</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" s="5" t="n">
+        <v>13.925</v>
+      </c>
+      <c r="I143" s="5" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="J143" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M143" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="N143" s="5" t="n">
+        <v>13.842</v>
+      </c>
+      <c r="O143" s="5" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23447,7 +23607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I142"/>
+  <dimension ref="A1:I143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -27887,6 +28047,37 @@
         <v>0.84</v>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="n">
+        <v>4.413</v>
+      </c>
+      <c r="C143" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D143" s="5" t="n">
+        <v>3.363</v>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>42.337</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H143" s="5" t="n">
+        <v>19.833</v>
+      </c>
+      <c r="I143" s="5" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O143"/>
+  <dimension ref="A1:O144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7540,6 +7540,55 @@
         <v>0.66</v>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="n">
+        <v>61.267</v>
+      </c>
+      <c r="C144" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D144" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="E144" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>82.87</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H144" s="5" t="n">
+        <v>13.925</v>
+      </c>
+      <c r="I144" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" s="5" t="n">
+        <v>47.107</v>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M144" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" s="5" t="n">
+        <v>13.842</v>
+      </c>
+      <c r="O144" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7551,7 +7600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I143"/>
+  <dimension ref="A1:I144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12022,6 +12071,37 @@
         <v>0.84</v>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="n">
+        <v>4.413</v>
+      </c>
+      <c r="C144" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D144" s="5" t="n">
+        <v>3.363</v>
+      </c>
+      <c r="E144" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>42.337</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H144" s="5" t="n">
+        <v>19.833</v>
+      </c>
+      <c r="I144" s="5" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12033,7 +12113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I143"/>
+  <dimension ref="A1:I144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16504,6 +16584,37 @@
         <v>0.84</v>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="n">
+        <v>4.413</v>
+      </c>
+      <c r="C144" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D144" s="5" t="n">
+        <v>3.363</v>
+      </c>
+      <c r="E144" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>42.337</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H144" s="5" t="n">
+        <v>19.833</v>
+      </c>
+      <c r="I144" s="5" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16515,7 +16626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O143"/>
+  <dimension ref="A1:O144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -23596,6 +23707,55 @@
         <v>0.66</v>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="n">
+        <v>61.267</v>
+      </c>
+      <c r="C144" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D144" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="E144" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>82.87</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H144" s="5" t="n">
+        <v>13.925</v>
+      </c>
+      <c r="I144" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" s="5" t="n">
+        <v>47.107</v>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M144" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" s="5" t="n">
+        <v>13.842</v>
+      </c>
+      <c r="O144" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23607,7 +23767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I143"/>
+  <dimension ref="A1:I144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -28078,6 +28238,37 @@
         <v>0.84</v>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="n">
+        <v>4.413</v>
+      </c>
+      <c r="C144" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D144" s="5" t="n">
+        <v>3.363</v>
+      </c>
+      <c r="E144" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>42.337</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H144" s="5" t="n">
+        <v>19.833</v>
+      </c>
+      <c r="I144" s="5" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O144"/>
+  <dimension ref="A1:O145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7589,6 +7589,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="n">
+        <v>61.333</v>
+      </c>
+      <c r="C145" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D145" s="5" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>82.623</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>13.825</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="J145" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M145" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" s="5" t="n">
+        <v>13.842</v>
+      </c>
+      <c r="O145" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7600,7 +7649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I144"/>
+  <dimension ref="A1:I145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12102,6 +12151,37 @@
         <v>0.84</v>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="n">
+        <v>4.383</v>
+      </c>
+      <c r="C145" s="5" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="D145" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>42.726</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>19.933</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12113,7 +12193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I144"/>
+  <dimension ref="A1:I145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16615,6 +16695,37 @@
         <v>0.84</v>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="n">
+        <v>4.383</v>
+      </c>
+      <c r="C145" s="5" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="D145" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>42.726</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>19.933</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16626,7 +16737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O144"/>
+  <dimension ref="A1:O145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -23756,6 +23867,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="n">
+        <v>61.333</v>
+      </c>
+      <c r="C145" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D145" s="5" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>82.623</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>13.825</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="J145" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M145" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" s="5" t="n">
+        <v>13.842</v>
+      </c>
+      <c r="O145" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23767,7 +23927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I144"/>
+  <dimension ref="A1:I145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -28269,6 +28429,37 @@
         <v>0.84</v>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="n">
+        <v>4.383</v>
+      </c>
+      <c r="C145" s="5" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="D145" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>42.726</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>19.933</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O145"/>
+  <dimension ref="A1:O146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7638,6 +7638,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="n">
+        <v>61.333</v>
+      </c>
+      <c r="C146" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" s="5" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="E146" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>82.623</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" s="5" t="n">
+        <v>13.825</v>
+      </c>
+      <c r="I146" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="5" t="n">
+        <v>47.043</v>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>5.968</v>
+      </c>
+      <c r="M146" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="N146" s="5" t="n">
+        <v>13.842</v>
+      </c>
+      <c r="O146" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7649,7 +7698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I145"/>
+  <dimension ref="A1:I146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12182,6 +12231,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="n">
+        <v>4.383</v>
+      </c>
+      <c r="C146" s="5" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="D146" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="E146" s="5" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>42.726</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H146" s="5" t="n">
+        <v>19.933</v>
+      </c>
+      <c r="I146" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12193,7 +12273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I145"/>
+  <dimension ref="A1:I146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16726,6 +16806,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="n">
+        <v>4.383</v>
+      </c>
+      <c r="C146" s="5" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="D146" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="E146" s="5" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>42.726</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H146" s="5" t="n">
+        <v>19.933</v>
+      </c>
+      <c r="I146" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16737,7 +16848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O145"/>
+  <dimension ref="A1:O146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -23916,6 +24027,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="n">
+        <v>61.333</v>
+      </c>
+      <c r="C146" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" s="5" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="E146" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>82.623</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" s="5" t="n">
+        <v>13.825</v>
+      </c>
+      <c r="I146" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="5" t="n">
+        <v>47.043</v>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>5.968</v>
+      </c>
+      <c r="M146" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="N146" s="5" t="n">
+        <v>13.842</v>
+      </c>
+      <c r="O146" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23927,7 +24087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I145"/>
+  <dimension ref="A1:I146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -28460,6 +28620,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="n">
+        <v>4.383</v>
+      </c>
+      <c r="C146" s="5" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="D146" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="E146" s="5" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>42.726</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H146" s="5" t="n">
+        <v>19.933</v>
+      </c>
+      <c r="I146" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O146"/>
+  <dimension ref="A1:O147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7687,6 +7687,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="n">
+        <v>61.333</v>
+      </c>
+      <c r="C147" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" s="5" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E147" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>82.92</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H147" s="5" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="J147" s="5" t="n">
+        <v>46.864</v>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M147" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N147" s="5" t="n">
+        <v>13.936</v>
+      </c>
+      <c r="O147" s="5" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7698,7 +7747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I146"/>
+  <dimension ref="A1:I147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12262,6 +12311,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="n">
+        <v>4.383</v>
+      </c>
+      <c r="C147" s="5" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="D147" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="E147" s="5" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>42.726</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H147" s="5" t="n">
+        <v>19.933</v>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12273,7 +12353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I146"/>
+  <dimension ref="A1:I147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16837,6 +16917,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="n">
+        <v>4.383</v>
+      </c>
+      <c r="C147" s="5" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="D147" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="E147" s="5" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>42.726</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H147" s="5" t="n">
+        <v>19.933</v>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16848,7 +16959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O146"/>
+  <dimension ref="A1:O147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24076,6 +24187,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="n">
+        <v>61.333</v>
+      </c>
+      <c r="C147" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" s="5" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E147" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>82.92</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H147" s="5" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="J147" s="5" t="n">
+        <v>46.864</v>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M147" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N147" s="5" t="n">
+        <v>13.936</v>
+      </c>
+      <c r="O147" s="5" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24087,7 +24247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I146"/>
+  <dimension ref="A1:I147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -28651,6 +28811,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="n">
+        <v>4.383</v>
+      </c>
+      <c r="C147" s="5" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="D147" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="E147" s="5" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>42.726</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H147" s="5" t="n">
+        <v>19.933</v>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O147"/>
+  <dimension ref="A1:O148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7736,6 +7736,55 @@
         <v>0.34</v>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="n">
+        <v>61.833</v>
+      </c>
+      <c r="C148" s="5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D148" s="5" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E148" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F148" s="5" t="n">
+        <v>82.92</v>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" s="5" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="I148" s="5" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="J148" s="5" t="n">
+        <v>46.864</v>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M148" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" s="5" t="n">
+        <v>14.007</v>
+      </c>
+      <c r="O148" s="5" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7747,7 +7796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I147"/>
+  <dimension ref="A1:I148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12342,6 +12391,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="n">
+        <v>4.383</v>
+      </c>
+      <c r="C148" s="5" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="D148" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="E148" s="5" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F148" s="5" t="n">
+        <v>42.726</v>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H148" s="5" t="n">
+        <v>19.933</v>
+      </c>
+      <c r="I148" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12353,7 +12433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I147"/>
+  <dimension ref="A1:I148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16948,6 +17028,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="n">
+        <v>4.383</v>
+      </c>
+      <c r="C148" s="5" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="D148" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="E148" s="5" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F148" s="5" t="n">
+        <v>42.726</v>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H148" s="5" t="n">
+        <v>19.933</v>
+      </c>
+      <c r="I148" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16959,7 +17070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O147"/>
+  <dimension ref="A1:O148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24236,6 +24347,55 @@
         <v>0.34</v>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="n">
+        <v>61.833</v>
+      </c>
+      <c r="C148" s="5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D148" s="5" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E148" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F148" s="5" t="n">
+        <v>82.92</v>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" s="5" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="I148" s="5" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="J148" s="5" t="n">
+        <v>46.864</v>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M148" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" s="5" t="n">
+        <v>14.007</v>
+      </c>
+      <c r="O148" s="5" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24247,7 +24407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I147"/>
+  <dimension ref="A1:I148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -28842,6 +29002,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="n">
+        <v>4.383</v>
+      </c>
+      <c r="C148" s="5" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="D148" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="E148" s="5" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F148" s="5" t="n">
+        <v>42.726</v>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H148" s="5" t="n">
+        <v>19.933</v>
+      </c>
+      <c r="I148" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Memory_Daily_Report.xlsx
+++ b/Memory_Daily_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O148"/>
+  <dimension ref="A1:O149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7785,6 +7785,55 @@
         <v>0.51</v>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="C149" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D149" s="5" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E149" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>82.79600000000001</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="H149" s="5" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="I149" s="5" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="J149" s="5" t="n">
+        <v>46.864</v>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="M149" s="5" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="N149" s="5" t="n">
+        <v>14.078</v>
+      </c>
+      <c r="O149" s="5" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7796,7 +7845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I148"/>
+  <dimension ref="A1:I149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12422,6 +12471,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="n">
+        <v>4.383</v>
+      </c>
+      <c r="C149" s="5" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="D149" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="E149" s="5" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>42.726</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H149" s="5" t="n">
+        <v>19.933</v>
+      </c>
+      <c r="I149" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12433,7 +12513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I148"/>
+  <dimension ref="A1:I149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17059,6 +17139,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="n">
+        <v>4.383</v>
+      </c>
+      <c r="C149" s="5" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="D149" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="E149" s="5" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>42.726</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H149" s="5" t="n">
+        <v>19.933</v>
+      </c>
+      <c r="I149" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17070,7 +17181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O148"/>
+  <dimension ref="A1:O149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24396,6 +24507,55 @@
         <v>0.51</v>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="C149" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D149" s="5" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E149" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>82.79600000000001</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="H149" s="5" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="I149" s="5" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="J149" s="5" t="n">
+        <v>46.864</v>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="M149" s="5" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="N149" s="5" t="n">
+        <v>14.078</v>
+      </c>
+      <c r="O149" s="5" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24407,7 +24567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I148"/>
+  <dimension ref="A1:I149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -29033,6 +29193,37 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="n">
+        <v>4.383</v>
+      </c>
+      <c r="C149" s="5" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="D149" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="E149" s="5" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>42.726</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H149" s="5" t="n">
+        <v>19.933</v>
+      </c>
+      <c r="I149" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
